--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>137113596</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>137114866</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>137115295</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>137115769</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>137115798</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>137299532</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>137113068</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137114111</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137117083</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>137113596</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>137114866</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>137115295</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>137115769</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>137115798</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>137299532</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>137113068</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137114111</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137117083</v>
       </c>
       <c r="B12" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 2308-2023 artfynd.xlsx
+++ b/artfynd/A 2308-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137115842</v>
       </c>
       <c r="B2" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137302486</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>137113596</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>137114866</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>137115295</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>137115769</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>137115798</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>137299532</v>
       </c>
       <c r="B9" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>137113068</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137114111</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137117083</v>
       </c>
       <c r="B12" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137116341</v>
       </c>
       <c r="B13" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>137116412</v>
       </c>
       <c r="B14" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137116617</v>
       </c>
       <c r="B15" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137116746</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137116921</v>
       </c>
       <c r="B17" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137299264</v>
       </c>
       <c r="B18" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137299407</v>
       </c>
       <c r="B19" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>137301340</v>
       </c>
       <c r="B20" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137301497</v>
       </c>
       <c r="B21" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137301644</v>
       </c>
       <c r="B22" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137302340</v>
       </c>
       <c r="B23" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137114327</v>
       </c>
       <c r="B24" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
